--- a/output/pdf_financials_xlsx/AUR.H.xlsx
+++ b/output/pdf_financials_xlsx/AUR.H.xlsx
@@ -1360,7 +1360,7 @@
         <v>-0.13734</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.06451900000000001</v>
+        <v>-0.06451900000000001</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-0.059716</v>
@@ -1672,7 +1672,7 @@
         <v>-0.13734</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.06451900000000001</v>
+        <v>-0.06451900000000001</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-0.059716</v>
@@ -1864,7 +1864,7 @@
         <v>-0.13734</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.06451900000000001</v>
+        <v>-0.06451900000000001</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-0.059716</v>
@@ -2164,7 +2164,7 @@
         <v>-0.13734</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.06451900000000001</v>
+        <v>-0.06451900000000001</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.059716</v>
@@ -2292,7 +2292,7 @@
         <v>-0.13734</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.06451900000000001</v>
+        <v>-0.06451900000000001</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.059716</v>
@@ -2448,7 +2448,7 @@
         <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
@@ -6370,49 +6370,49 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.029032</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.496196</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.496834</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.496834</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.496834</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.496834</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.496834</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.496834</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.611804</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.611804</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.611804</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.611804</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.611804</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.611804</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>1.611804</v>
       </c>
     </row>
     <row r="93">
@@ -10036,7 +10036,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -10756,7 +10760,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -10845,7 +10853,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -11738,7 +11750,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -12534,7 +12550,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -21753,7 +21773,7 @@
         <v>-0.13734</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>0.06451900000000001</v>
+        <v>-0.06451900000000001</v>
       </c>
       <c r="M127" s="5" t="n">
         <v>-0.059716</v>

--- a/output/pdf_financials_xlsx/AUR.H.xlsx
+++ b/output/pdf_financials_xlsx/AUR.H.xlsx
@@ -1092,34 +1092,34 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001359</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.009005000000000001</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.007698</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.006583</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.004305</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.003073</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.002838</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.004508</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.003766</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.000298</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
@@ -2152,34 +2152,34 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.607703</v>
+        <v>-0.609062</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.231719</v>
+        <v>-0.240724</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.158131</v>
+        <v>-1.165829</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.13734</v>
+        <v>-0.143923</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.06451900000000001</v>
+        <v>-0.068824</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.059716</v>
+        <v>-0.062789</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.059295</v>
+        <v>-0.062133</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.180834</v>
+        <v>-0.185342</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.05821</v>
+        <v>-0.061976</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.062003</v>
+        <v>-0.062301</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-0.063139</v>
@@ -2280,34 +2280,34 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.607703</v>
+        <v>-0.609062</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.231719</v>
+        <v>-0.240724</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.158131</v>
+        <v>-1.165829</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.13734</v>
+        <v>-0.143923</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.06451900000000001</v>
+        <v>-0.068824</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.059716</v>
+        <v>-0.062789</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.059295</v>
+        <v>-0.062133</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.180834</v>
+        <v>-0.185342</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.05821</v>
+        <v>-0.061976</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.062003</v>
+        <v>-0.062301</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-0.063139</v>
@@ -2624,19 +2624,19 @@
         <v>0.237495</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.112716</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.046909</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.018132</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.010146</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.003471</v>
       </c>
     </row>
     <row r="35">
@@ -2748,19 +2748,19 @@
         <v>0.237495</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.112716</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.046909</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.018132</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.010146</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.003471</v>
       </c>
     </row>
     <row r="37">
@@ -3492,16 +3492,16 @@
         <v>0.001891</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.114607</v>
+        <v>0.001891</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.051142</v>
+        <v>0.004233</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.0189</v>
+        <v>0.000768</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.010923</v>
+        <v>0.000777</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>0</v>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -22756,7 +22756,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -24154,7 +24154,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">

--- a/output/pdf_financials_xlsx/AUR.H.xlsx
+++ b/output/pdf_financials_xlsx/AUR.H.xlsx
@@ -4532,16 +4532,16 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.022089</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.002967</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.004077</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.000286</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
         <v>0.012286</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.037089</v>
+        <v>0.059178</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.017967</v>
+        <v>0.020934</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.023717</v>
+        <v>0.027794</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0.012286</v>
@@ -6913,10 +6913,10 @@
         <v>0.00339</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.001471</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000117</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>0</v>
@@ -16752,7 +16752,11 @@
           <t>HST Recoverable</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
